--- a/Data/Key_items.xlsx
+++ b/Data/Key_items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/05c776d51af9edc4/Work-related/VS - Code project/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="11_F25DC773A252ABDACC10485F719957D85BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A681423-78F5-244B-8FCE-F701A05DBD95}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="11_F25DC773A252ABDACC10485F719957D85BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B127D508-1611-6045-ABDF-1B657C081888}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>KeyCode</t>
   </si>
@@ -228,6 +228,12 @@
   </si>
   <si>
     <t>Overdue_loan</t>
+  </si>
+  <si>
+    <t>Fees Income</t>
+  </si>
+  <si>
+    <t>IS.6</t>
   </si>
 </sst>
 </file>
@@ -558,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
@@ -821,6 +827,14 @@
         <v>63</v>
       </c>
     </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/Key_items.xlsx
+++ b/Data/Key_items.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10824"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/05c776d51af9edc4/Work-related/VS - Code project/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="11_F25DC773A252ABDACC10485F719957D85BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B127D508-1611-6045-ABDF-1B657C081888}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="11_F25DC773A252ABDACC10485F719957D85BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E692C79-FD23-1A47-A424-821160A50E6E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>KeyCode</t>
   </si>
@@ -201,9 +201,6 @@
   </si>
   <si>
     <t>CA.25</t>
-  </si>
-  <si>
-    <t>NPL Formation (%)</t>
   </si>
   <si>
     <t>G2 Formation (%)</t>
@@ -655,16 +652,13 @@
       <c r="A11" t="s">
         <v>53</v>
       </c>
-      <c r="B11" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -685,7 +679,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
         <v>51</v>
@@ -805,34 +799,34 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" t="s">
         <v>58</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
         <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
         <v>62</v>
-      </c>
-      <c r="B32" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Key_items.xlsx
+++ b/Data/Key_items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/05c776d51af9edc4/Work-related/VS - Code project/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="11_F25DC773A252ABDACC10485F719957D85BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E692C79-FD23-1A47-A424-821160A50E6E}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="11_F25DC773A252ABDACC10485F719957D85BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46591213-EF64-954C-8CC5-BA0BAF19C7DA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>KeyCode</t>
   </si>
@@ -203,9 +203,6 @@
     <t>CA.25</t>
   </si>
   <si>
-    <t>G2 Formation (%)</t>
-  </si>
-  <si>
     <t>BS.13</t>
   </si>
   <si>
@@ -231,6 +228,12 @@
   </si>
   <si>
     <t>IS.6</t>
+  </si>
+  <si>
+    <t>New NPL</t>
+  </si>
+  <si>
+    <t>New G2</t>
   </si>
 </sst>
 </file>
@@ -652,13 +655,16 @@
       <c r="A11" t="s">
         <v>53</v>
       </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -679,7 +685,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
         <v>51</v>
@@ -799,34 +805,34 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
         <v>57</v>
-      </c>
-      <c r="B30" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
         <v>59</v>
-      </c>
-      <c r="B31" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
         <v>61</v>
-      </c>
-      <c r="B32" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
